--- a/data/trans_dic/IP09-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP09-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen actualmente esa dolencia, enfermedad o impedimento que le ha limitado de forma continuada (más de 10 días en los últimos 12 meses)</t>
+          <t>Menores que padecen actualmente esa dolencia, enfermedad o impedimento que le ha limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,71; 59,76</t>
+          <t>7,36; 60,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,54; 65,3</t>
+          <t>19,49; 66,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,37; 72,93</t>
+          <t>13,97; 71,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,63; 57,14</t>
+          <t>12,46; 58,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,49; 45,69</t>
+          <t>7,45; 41,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,9; 59,69</t>
+          <t>20,08; 61,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,8; 70,78</t>
+          <t>22,33; 73,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,35; 44,81</t>
+          <t>4,12; 45,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,52; 40,39</t>
+          <t>12,05; 40,3</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24,68; 53,73</t>
+          <t>24,44; 53,95</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25,18; 65,24</t>
+          <t>23,47; 61,39</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,17; 40,42</t>
+          <t>8,04; 42,89</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,11; 46,97</t>
+          <t>11,25; 45,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,58; 52,11</t>
+          <t>23,09; 51,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,67; 57,07</t>
+          <t>22,76; 58,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,74; 83,73</t>
+          <t>23,82; 84,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,25; 49,7</t>
+          <t>18,95; 49,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,06; 42,36</t>
+          <t>15,27; 43,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,97; 59,58</t>
+          <t>23,55; 59,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,99; 59,08</t>
+          <t>27,34; 60,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,73; 42,57</t>
+          <t>20,92; 41,82</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23,39; 43,13</t>
+          <t>22,93; 42,46</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28,19; 53,62</t>
+          <t>26,59; 52,33</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,12; 65,76</t>
+          <t>31,67; 66,42</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,76; 70,59</t>
+          <t>16,05; 70,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,22; 57,15</t>
+          <t>22,31; 56,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,46; 59,44</t>
+          <t>12,59; 57,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,53; 53,15</t>
+          <t>13,11; 58,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,6; 35,43</t>
+          <t>4,22; 38,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,53; 55,26</t>
+          <t>25,01; 55,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,19; 72,2</t>
+          <t>21,44; 75,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,66; 52,44</t>
+          <t>12,14; 52,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,65; 41,21</t>
+          <t>13,39; 41,95</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28,52; 51,55</t>
+          <t>28,08; 51,2</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24,83; 58,11</t>
+          <t>24,17; 59,8</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,61; 47,89</t>
+          <t>17,13; 46,64</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,08; 26,15</t>
+          <t>3,08; 28,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,08; 42,11</t>
+          <t>10,27; 42,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,75; 74,69</t>
+          <t>22,95; 77,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,32; 52,49</t>
+          <t>13,96; 53,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,74; 53,42</t>
+          <t>20,78; 51,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,36; 46,49</t>
+          <t>17,15; 45,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,22; 78,4</t>
+          <t>33,59; 78,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,02; 43,2</t>
+          <t>13,68; 42,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,68; 35,35</t>
+          <t>13,56; 34,84</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,29; 39,45</t>
+          <t>16,94; 38,49</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33,07; 69,54</t>
+          <t>35,76; 70,42</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,26; 40,12</t>
+          <t>17,99; 40,43</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,34; 32,43</t>
+          <t>15,2; 33,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,05; 42,84</t>
+          <t>26,84; 43,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,68; 52,38</t>
+          <t>29,11; 51,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,7; 56,99</t>
+          <t>27,69; 58,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,67; 36,82</t>
+          <t>21,42; 37,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,05; 42,65</t>
+          <t>26,02; 41,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,37; 58,14</t>
+          <t>34,37; 56,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,61; 39,25</t>
+          <t>19,14; 39,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,95; 33,06</t>
+          <t>20,57; 32,23</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28,93; 40,34</t>
+          <t>28,31; 40,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35,85; 52,0</t>
+          <t>34,9; 50,98</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,71; 42,58</t>
+          <t>25,88; 43,54</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen actualmente esa dolencia, enfermedad o impedimento que le ha limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2860</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5621</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3254</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4053</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3999</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6901</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>4386</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>4507</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>6859</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>12522</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>7640</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>8560</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>719; 5879</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2741; 9419</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1141; 5801</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1495; 7024</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1306; 7237</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3619; 11104</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2168; 7154</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>987; 10783</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>3289; 11003</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>7844; 17314</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4195; 10976</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2889; 15413</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>4337</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10088</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7779</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10702</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>9403</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>8928</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>7945</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>11305</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>13740</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>19016</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>15723</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>22007</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1767; 7173</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>6420; 14268</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4460; 11549</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>5087; 18006</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>5375; 13988</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>4797; 13549</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>4720; 11907</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>7090; 15765</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>9218; 18425</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>13583; 25147</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>10540; 20742</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>14979; 31413</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3130</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7633</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2886</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4265</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2653</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>10112</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4323</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>6484</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>5783</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>17745</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>7209</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>10749</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1263; 5568</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4434; 11299</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1134; 5168</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1801; 7988</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>649; 5897</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6326; 14050</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1944; 6875</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2544; 10927</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3111; 9748</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>12683; 23123</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>4370; 10810</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>5945; 16186</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2474</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5056</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5159</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4882</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>7986</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>8311</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>7121</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>7304</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>10459</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>13366</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>12279</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>12186</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>705; 6475</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2169; 9005</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2375; 8013</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2187; 8320</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>4616; 11414</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>4745; 12531</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>4242; 9886</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>3859; 12040</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>6119; 15724</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>8267; 18785</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>8218; 16182</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>7894; 17737</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>12800</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>28397</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>19077</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>23901</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>24042</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>34252</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>23775</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>29601</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>36842</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>62649</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>42852</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>53502</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>8551; 18823</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>22240; 35877</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>13716; 24245</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>17385; 37000</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>17885; 31518</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>26651; 42342</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>17685; 29248</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>18953; 38918</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>28746; 45033</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>52464; 74221</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>34396; 50248</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>41883; 70448</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP09-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP09-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,36; 60,21</t>
+          <t>7,76; 58,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,49; 66,97</t>
+          <t>20,43; 64,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,97; 71,02</t>
+          <t>13,58; 71,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,46; 58,51</t>
+          <t>15,02; 57,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,45; 41,27</t>
+          <t>10,77; 41,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,08; 61,6</t>
+          <t>19,14; 60,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,33; 73,69</t>
+          <t>22,24; 73,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,12; 45,06</t>
+          <t>3,75; 43,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,05; 40,3</t>
+          <t>13,06; 40,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24,44; 53,95</t>
+          <t>23,34; 52,77</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23,47; 61,39</t>
+          <t>23,84; 62,92</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,04; 42,89</t>
+          <t>7,51; 40,6</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,25; 45,7</t>
+          <t>11,81; 46,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,09; 51,31</t>
+          <t>21,75; 51,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,76; 58,93</t>
+          <t>23,96; 57,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,82; 84,3</t>
+          <t>22,88; 81,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,95; 49,32</t>
+          <t>19,09; 47,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,27; 43,12</t>
+          <t>15,98; 42,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,55; 59,41</t>
+          <t>22,51; 58,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,34; 60,79</t>
+          <t>27,57; 61,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,92; 41,82</t>
+          <t>20,81; 43,09</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22,93; 42,46</t>
+          <t>22,92; 42,58</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26,59; 52,33</t>
+          <t>28,08; 54,63</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,67; 66,42</t>
+          <t>32,58; 65,75</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,05; 70,76</t>
+          <t>15,83; 64,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,31; 56,86</t>
+          <t>22,13; 55,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,59; 57,37</t>
+          <t>12,11; 60,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,11; 58,12</t>
+          <t>13,73; 54,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,22; 38,37</t>
+          <t>4,33; 38,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,01; 55,55</t>
+          <t>23,92; 56,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,44; 75,81</t>
+          <t>22,02; 73,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,14; 52,13</t>
+          <t>13,4; 55,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,39; 41,95</t>
+          <t>13,46; 41,28</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28,08; 51,2</t>
+          <t>27,68; 52,23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24,17; 59,8</t>
+          <t>22,35; 58,15</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,13; 46,64</t>
+          <t>17,31; 48,59</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,08; 28,26</t>
+          <t>3,06; 27,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,27; 42,62</t>
+          <t>10,37; 42,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,95; 77,42</t>
+          <t>23,85; 77,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,96; 53,09</t>
+          <t>14,81; 52,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,78; 51,38</t>
+          <t>20,52; 51,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,15; 45,28</t>
+          <t>17,29; 46,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,59; 78,28</t>
+          <t>30,52; 77,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,68; 42,69</t>
+          <t>13,1; 41,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,56; 34,84</t>
+          <t>14,12; 35,42</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16,94; 38,49</t>
+          <t>18,81; 39,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35,76; 70,42</t>
+          <t>35,01; 70,41</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,99; 40,43</t>
+          <t>16,84; 39,89</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,2; 33,47</t>
+          <t>14,64; 33,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,84; 43,29</t>
+          <t>26,58; 43,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,11; 51,45</t>
+          <t>29,7; 52,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27,69; 58,93</t>
+          <t>27,16; 56,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,42; 37,76</t>
+          <t>21,85; 38,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,02; 41,34</t>
+          <t>26,19; 41,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,37; 56,85</t>
+          <t>35,03; 57,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,14; 39,3</t>
+          <t>20,14; 40,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,57; 32,23</t>
+          <t>20,38; 33,08</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28,31; 40,06</t>
+          <t>28,71; 40,23</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34,9; 50,98</t>
+          <t>35,99; 52,31</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,88; 43,54</t>
+          <t>24,71; 42,72</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>719; 5879</t>
+          <t>758; 5700</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2741; 9419</t>
+          <t>2873; 9080</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1141; 5801</t>
+          <t>1109; 5846</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1495; 7024</t>
+          <t>1803; 6901</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1306; 7237</t>
+          <t>1888; 7217</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3619; 11104</t>
+          <t>3451; 10872</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2168; 7154</t>
+          <t>2159; 7099</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>987; 10783</t>
+          <t>898; 10452</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3289; 11003</t>
+          <t>3567; 11006</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7844; 17314</t>
+          <t>7489; 16937</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4195; 10976</t>
+          <t>4262; 11249</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2889; 15413</t>
+          <t>2701; 14591</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1767; 7173</t>
+          <t>1853; 7360</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6420; 14268</t>
+          <t>6048; 14303</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4460; 11549</t>
+          <t>4695; 11360</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5087; 18006</t>
+          <t>4888; 17313</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5375; 13988</t>
+          <t>5414; 13536</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4797; 13549</t>
+          <t>5022; 13413</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4720; 11907</t>
+          <t>4511; 11788</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7090; 15765</t>
+          <t>7150; 16034</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9218; 18425</t>
+          <t>9166; 18984</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13583; 25147</t>
+          <t>13574; 25220</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10540; 20742</t>
+          <t>11129; 21654</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14979; 31413</t>
+          <t>15410; 31098</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1263; 5568</t>
+          <t>1246; 5055</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4434; 11299</t>
+          <t>4396; 11103</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1134; 5168</t>
+          <t>1091; 5428</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1801; 7988</t>
+          <t>1887; 7480</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>649; 5897</t>
+          <t>665; 5875</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6326; 14050</t>
+          <t>6051; 14267</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1944; 6875</t>
+          <t>1997; 6645</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2544; 10927</t>
+          <t>2808; 11587</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3111; 9748</t>
+          <t>3128; 9591</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12683; 23123</t>
+          <t>12500; 23588</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4370; 10810</t>
+          <t>4040; 10512</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5945; 16186</t>
+          <t>6008; 16862</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>705; 6475</t>
+          <t>702; 6279</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2169; 9005</t>
+          <t>2191; 8989</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2375; 8013</t>
+          <t>2468; 7983</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2187; 8320</t>
+          <t>2321; 8172</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4616; 11414</t>
+          <t>4560; 11418</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4745; 12531</t>
+          <t>4786; 12842</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4242; 9886</t>
+          <t>3854; 9838</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3859; 12040</t>
+          <t>3694; 11652</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6119; 15724</t>
+          <t>6371; 15986</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8267; 18785</t>
+          <t>9181; 19464</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8218; 16182</t>
+          <t>8044; 16178</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7894; 17737</t>
+          <t>7387; 17501</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8551; 18823</t>
+          <t>8235; 18927</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22240; 35877</t>
+          <t>22023; 35934</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13716; 24245</t>
+          <t>13995; 24775</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17385; 37000</t>
+          <t>17052; 35165</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>17885; 31518</t>
+          <t>18238; 31815</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26651; 42342</t>
+          <t>26828; 42523</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17685; 29248</t>
+          <t>18024; 29737</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>18953; 38918</t>
+          <t>19946; 39888</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>28746; 45033</t>
+          <t>28478; 46224</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>52464; 74221</t>
+          <t>53194; 74540</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>34396; 50248</t>
+          <t>35470; 51558</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>41883; 70448</t>
+          <t>39976; 69126</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP09-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP09-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>22,81%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>38,28%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>45,18%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20,01%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>29,28%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>39,96%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>39,83%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>33,76%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>22,81%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>38,28%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>45,18%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>25,64%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,76; 58,38</t>
+          <t>8,49; 45,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,43; 64,56</t>
+          <t>19,9; 59,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,58; 71,57</t>
+          <t>15,8; 70,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,02; 57,48</t>
+          <t>4,16; 45,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,77; 41,15</t>
+          <t>7,71; 59,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,14; 60,31</t>
+          <t>17,54; 65,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,24; 73,12</t>
+          <t>14,37; 72,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,75; 43,67</t>
+          <t>13,14; 58,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,06; 40,31</t>
+          <t>12,52; 40,39</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23,34; 52,77</t>
+          <t>24,68; 53,73</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23,84; 62,92</t>
+          <t>25,18; 65,24</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,51; 40,6</t>
+          <t>9,41; 42,06</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>33,16%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28,41%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>39,64%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>46,37%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>27,63%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>36,28%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>39,69%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>50,1%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>33,16%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>28,41%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>39,64%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>42,39%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,81; 46,89</t>
+          <t>21,25; 49,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,75; 51,44</t>
+          <t>14,06; 42,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,96; 57,97</t>
+          <t>23,97; 59,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,88; 81,06</t>
+          <t>29,11; 62,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,09; 47,73</t>
+          <t>12,11; 46,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,98; 42,69</t>
+          <t>24,58; 52,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,51; 58,82</t>
+          <t>22,67; 57,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,57; 61,82</t>
+          <t>18,73; 59,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,81; 43,09</t>
+          <t>19,73; 42,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22,92; 42,58</t>
+          <t>23,39; 43,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28,08; 54,63</t>
+          <t>28,19; 53,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,58; 65,75</t>
+          <t>29,71; 55,53</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>17,27%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>39,98%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>47,67%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>31,17%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>39,77%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>38,41%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>32,04%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>31,03%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>17,27%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>39,98%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>47,67%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,52%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,83; 64,24</t>
+          <t>4,6; 35,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,13; 55,88</t>
+          <t>24,53; 55,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,11; 60,26</t>
+          <t>24,19; 72,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,73; 54,43</t>
+          <t>12,42; 52,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,33; 38,23</t>
+          <t>15,76; 70,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,92; 56,41</t>
+          <t>22,22; 57,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,02; 73,28</t>
+          <t>12,46; 59,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,4; 55,28</t>
+          <t>12,54; 53,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,46; 41,28</t>
+          <t>11,65; 41,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27,68; 52,23</t>
+          <t>28,52; 51,55</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22,35; 58,15</t>
+          <t>24,83; 58,11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,31; 48,59</t>
+          <t>16,87; 47,5</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>35,95%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>30,03%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>56,39%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>26,15%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>10,8%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>23,93%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>49,84%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>31,15%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>35,95%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>30,03%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>56,39%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,62%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,06; 27,4</t>
+          <t>20,74; 53,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,37; 42,54</t>
+          <t>17,36; 46,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,85; 77,13</t>
+          <t>32,22; 78,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,81; 52,14</t>
+          <t>14,23; 42,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,52; 51,4</t>
+          <t>3,08; 26,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,29; 46,4</t>
+          <t>10,08; 42,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,52; 77,9</t>
+          <t>22,75; 74,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,1; 41,31</t>
+          <t>14,0; 51,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,12; 35,42</t>
+          <t>14,68; 35,35</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,81; 39,88</t>
+          <t>18,29; 39,45</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35,01; 70,41</t>
+          <t>33,07; 69,54</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,84; 39,89</t>
+          <t>17,58; 40,16</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>28,8%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>33,44%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>46,21%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>31,15%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>22,76%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>34,27%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>40,48%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>38,07%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>28,8%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>33,44%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>46,21%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>31,8%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,64; 33,65</t>
+          <t>21,67; 36,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,58; 43,36</t>
+          <t>26,05; 42,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,7; 52,57</t>
+          <t>35,37; 58,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27,16; 56,01</t>
+          <t>19,96; 40,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,85; 38,11</t>
+          <t>14,34; 32,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,19; 41,52</t>
+          <t>26,05; 42,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,03; 57,8</t>
+          <t>29,68; 52,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>20,14; 40,28</t>
+          <t>22,96; 42,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,38; 33,08</t>
+          <t>20,95; 33,06</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28,71; 40,23</t>
+          <t>28,93; 40,34</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35,99; 52,31</t>
+          <t>35,85; 52,0</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,71; 42,72</t>
+          <t>24,58; 39,54</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3999</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6901</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4386</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4129</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>2860</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>5621</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>3254</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4053</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3999</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6901</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4386</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4507</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8560</t>
+          <t>8499</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>758; 5700</t>
+          <t>1489; 8012</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2873; 9080</t>
+          <t>3587; 10761</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1109; 5846</t>
+          <t>1534; 6872</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1803; 6901</t>
+          <t>858; 9425</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1888; 7217</t>
+          <t>753; 5836</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3451; 10872</t>
+          <t>2466; 9184</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2159; 7099</t>
+          <t>1174; 5958</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>898; 10452</t>
+          <t>1644; 7381</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3567; 11006</t>
+          <t>3419; 11029</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7489; 16937</t>
+          <t>7919; 17244</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4262; 11249</t>
+          <t>4501; 11663</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2701; 14591</t>
+          <t>3120; 13939</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9403</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8928</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7945</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10807</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>4337</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>10088</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>7779</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10702</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9403</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8928</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7945</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11305</t>
+          <t>5919</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22007</t>
+          <t>16726</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1853; 7360</t>
+          <t>6027; 14095</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6048; 14303</t>
+          <t>4419; 13310</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4695; 11360</t>
+          <t>4804; 11941</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4888; 17313</t>
+          <t>6784; 14616</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5414; 13536</t>
+          <t>1900; 7372</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5022; 13413</t>
+          <t>6836; 14490</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4511; 11788</t>
+          <t>4442; 11184</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7150; 16034</t>
+          <t>3024; 9554</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9166; 18984</t>
+          <t>8691; 18753</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13574; 25220</t>
+          <t>13851; 25546</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11129; 21654</t>
+          <t>11174; 21254</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15410; 31098</t>
+          <t>11723; 21908</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2653</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10112</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4323</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6190</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>3130</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>7633</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>2886</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4265</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2653</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>10112</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4323</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6484</t>
+          <t>4126</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10749</t>
+          <t>10315</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1246; 5055</t>
+          <t>707; 5444</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4396; 11103</t>
+          <t>6204; 13977</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1091; 5428</t>
+          <t>2194; 6547</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1887; 7480</t>
+          <t>2466; 10466</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>665; 5875</t>
+          <t>1240; 5554</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6051; 14267</t>
+          <t>4415; 11356</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1997; 6645</t>
+          <t>1123; 5354</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2808; 11587</t>
+          <t>1748; 7451</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3128; 9591</t>
+          <t>2708; 9575</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12500; 23588</t>
+          <t>12882; 23281</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4040; 10512</t>
+          <t>4488; 10504</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6008; 16862</t>
+          <t>5702; 16055</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>7986</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8311</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7121</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6556</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>2474</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>5056</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>5159</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4882</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>7986</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>8311</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>7121</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7304</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12186</t>
+          <t>11251</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>702; 6279</t>
+          <t>4608; 11867</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2191; 8989</t>
+          <t>4803; 12868</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2468; 7983</t>
+          <t>4070; 9901</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2321; 8172</t>
+          <t>3568; 10704</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4560; 11418</t>
+          <t>705; 5992</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4786; 12842</t>
+          <t>2129; 8897</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3854; 9838</t>
+          <t>2354; 7731</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3694; 11652</t>
+          <t>2192; 8112</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6371; 15986</t>
+          <t>6623; 15952</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9181; 19464</t>
+          <t>8926; 19255</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8044; 16178</t>
+          <t>7600; 15980</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7387; 17501</t>
+          <t>7161; 16360</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>24042</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>34252</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>23775</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>27682</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>12800</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>28397</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>19077</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>23901</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>24042</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>34252</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>23775</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>29601</t>
+          <t>19110</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>53502</t>
+          <t>46792</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8235; 18927</t>
+          <t>18092; 30739</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22023; 35934</t>
+          <t>26680; 43680</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13995; 24775</t>
+          <t>18195; 29911</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17052; 35165</t>
+          <t>17739; 36240</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>18238; 31815</t>
+          <t>8067; 18237</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26828; 42523</t>
+          <t>21589; 35499</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18024; 29737</t>
+          <t>13988; 24681</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>19946; 39888</t>
+          <t>13376; 24933</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>28478; 46224</t>
+          <t>29266; 46196</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>53194; 74540</t>
+          <t>53598; 74753</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35470; 51558</t>
+          <t>35337; 51256</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>39976; 69126</t>
+          <t>36173; 58177</t>
         </is>
       </c>
     </row>
